--- a/artfynd/A 6098-2026 artfynd.xlsx
+++ b/artfynd/A 6098-2026 artfynd.xlsx
@@ -3839,7 +3839,7 @@
         <v>131674866</v>
       </c>
       <c r="B33" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>131674867</v>
       </c>
       <c r="B34" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 6098-2026 artfynd.xlsx
+++ b/artfynd/A 6098-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131674890</v>
+        <v>135298248</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458690</v>
+        <v>458859</v>
       </c>
       <c r="R2" t="n">
-        <v>6783647</v>
+        <v>6783626</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,23 +766,43 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131674901</v>
+        <v>131674890</v>
       </c>
       <c r="B3" t="n">
         <v>79373</v>
@@ -807,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458843</v>
+        <v>458690</v>
       </c>
       <c r="R3" t="n">
-        <v>6783622</v>
+        <v>6783647</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131674902</v>
+        <v>131674901</v>
       </c>
       <c r="B4" t="n">
         <v>79373</v>
@@ -904,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458812</v>
+        <v>458843</v>
       </c>
       <c r="R4" t="n">
-        <v>6783576</v>
+        <v>6783622</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131674904</v>
+        <v>131674902</v>
       </c>
       <c r="B5" t="n">
         <v>79373</v>
@@ -1001,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458628</v>
+        <v>458812</v>
       </c>
       <c r="R5" t="n">
-        <v>6783528</v>
+        <v>6783576</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131674905</v>
+        <v>131674904</v>
       </c>
       <c r="B6" t="n">
         <v>79373</v>
@@ -1098,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458618</v>
+        <v>458628</v>
       </c>
       <c r="R6" t="n">
-        <v>6783506</v>
+        <v>6783528</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131674906</v>
+        <v>131674905</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1195,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458582</v>
+        <v>458618</v>
       </c>
       <c r="R7" t="n">
-        <v>6783476</v>
+        <v>6783506</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131674907</v>
+        <v>131674906</v>
       </c>
       <c r="B8" t="n">
         <v>79373</v>
@@ -1292,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458562</v>
+        <v>458582</v>
       </c>
       <c r="R8" t="n">
-        <v>6783460</v>
+        <v>6783476</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,7 +1384,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131674908</v>
+        <v>131674907</v>
       </c>
       <c r="B9" t="n">
         <v>79373</v>
@@ -1389,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458548</v>
+        <v>458562</v>
       </c>
       <c r="R9" t="n">
-        <v>6783447</v>
+        <v>6783460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131674909</v>
+        <v>131674908</v>
       </c>
       <c r="B10" t="n">
         <v>79373</v>
@@ -1486,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458526</v>
+        <v>458548</v>
       </c>
       <c r="R10" t="n">
-        <v>6783438</v>
+        <v>6783447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131674910</v>
+        <v>131674909</v>
       </c>
       <c r="B11" t="n">
         <v>79373</v>
@@ -1583,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458917</v>
+        <v>458526</v>
       </c>
       <c r="R11" t="n">
-        <v>6783639</v>
+        <v>6783438</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131674911</v>
+        <v>131674910</v>
       </c>
       <c r="B12" t="n">
         <v>79373</v>
@@ -1680,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458855</v>
+        <v>458917</v>
       </c>
       <c r="R12" t="n">
-        <v>6783589</v>
+        <v>6783639</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,48 +1772,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131674866</v>
+        <v>131674911</v>
       </c>
       <c r="B13" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458846</v>
+        <v>458855</v>
       </c>
       <c r="R13" t="n">
-        <v>6783602</v>
+        <v>6783589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1824,7 +1851,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1843,51 +1869,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131674867</v>
+        <v>135298242</v>
       </c>
       <c r="B14" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458832</v>
+        <v>458642</v>
       </c>
       <c r="R14" t="n">
-        <v>6783615</v>
+        <v>6783514</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1911,12 +1934,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1925,67 +1958,86 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131674773</v>
+        <v>135298247</v>
       </c>
       <c r="B15" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458794</v>
+        <v>458859</v>
       </c>
       <c r="R15" t="n">
-        <v>6783576</v>
+        <v>6783622</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2009,12 +2061,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2025,58 +2087,73 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131674821</v>
+        <v>131674866</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>79130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2084,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458804</v>
+        <v>458846</v>
       </c>
       <c r="R16" t="n">
-        <v>6783648</v>
+        <v>6783602</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2128,6 +2205,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2146,42 +2224,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131674827</v>
+        <v>131674867</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>79130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2189,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458883</v>
+        <v>458832</v>
       </c>
       <c r="R17" t="n">
-        <v>6783596</v>
+        <v>6783615</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2233,6 +2306,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2251,53 +2325,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131674828</v>
+        <v>131674773</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458856</v>
+        <v>458794</v>
       </c>
       <c r="R18" t="n">
-        <v>6783589</v>
+        <v>6783576</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2356,7 +2422,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131674829</v>
+        <v>131674821</v>
       </c>
       <c r="B19" t="n">
         <v>57972</v>
@@ -2399,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458713</v>
+        <v>458804</v>
       </c>
       <c r="R19" t="n">
-        <v>6783543</v>
+        <v>6783648</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2461,7 +2527,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131674830</v>
+        <v>131674827</v>
       </c>
       <c r="B20" t="n">
         <v>57972</v>
@@ -2504,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458616</v>
+        <v>458883</v>
       </c>
       <c r="R20" t="n">
-        <v>6783487</v>
+        <v>6783596</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,7 +2632,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131674832</v>
+        <v>131674828</v>
       </c>
       <c r="B21" t="n">
         <v>57972</v>
@@ -2599,7 +2665,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2609,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458582</v>
+        <v>458856</v>
       </c>
       <c r="R21" t="n">
-        <v>6783476</v>
+        <v>6783589</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2671,7 +2737,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131674833</v>
+        <v>131674829</v>
       </c>
       <c r="B22" t="n">
         <v>57972</v>
@@ -2704,7 +2770,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2714,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458552</v>
+        <v>458713</v>
       </c>
       <c r="R22" t="n">
-        <v>6783452</v>
+        <v>6783543</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,7 +2842,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131674841</v>
+        <v>131674830</v>
       </c>
       <c r="B23" t="n">
         <v>57972</v>
@@ -2809,7 +2875,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2819,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458778</v>
+        <v>458616</v>
       </c>
       <c r="R23" t="n">
-        <v>6783537</v>
+        <v>6783487</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2881,27 +2947,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131674795</v>
+        <v>131674832</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2914,7 +2980,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2924,10 +2990,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458501</v>
+        <v>458582</v>
       </c>
       <c r="R24" t="n">
-        <v>6783418</v>
+        <v>6783476</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,10 +3052,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131674799</v>
+        <v>131674833</v>
       </c>
       <c r="B25" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,21 +3063,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3019,7 +3085,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3029,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458534</v>
+        <v>458552</v>
       </c>
       <c r="R25" t="n">
-        <v>6783516</v>
+        <v>6783452</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,10 +3157,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131674803</v>
+        <v>131674841</v>
       </c>
       <c r="B26" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,21 +3168,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3124,7 +3190,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3134,10 +3200,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458884</v>
+        <v>458778</v>
       </c>
       <c r="R26" t="n">
-        <v>6783621</v>
+        <v>6783537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3196,32 +3262,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131674804</v>
+        <v>131674795</v>
       </c>
       <c r="B27" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3229,7 +3295,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3239,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458703</v>
+        <v>458501</v>
       </c>
       <c r="R27" t="n">
-        <v>6783521</v>
+        <v>6783418</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3301,7 +3367,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131674807</v>
+        <v>131674799</v>
       </c>
       <c r="B28" t="n">
         <v>57162</v>
@@ -3334,7 +3400,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3344,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458847</v>
+        <v>458534</v>
       </c>
       <c r="R28" t="n">
-        <v>6783618</v>
+        <v>6783516</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3406,7 +3472,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131674808</v>
+        <v>131674803</v>
       </c>
       <c r="B29" t="n">
         <v>57162</v>
@@ -3449,10 +3515,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458647</v>
+        <v>458884</v>
       </c>
       <c r="R29" t="n">
-        <v>6783489</v>
+        <v>6783621</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3511,10 +3577,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131674845</v>
+        <v>131674804</v>
       </c>
       <c r="B30" t="n">
-        <v>57165</v>
+        <v>57162</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3522,21 +3588,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3544,7 +3610,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3554,10 +3620,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458496</v>
+        <v>458703</v>
       </c>
       <c r="R30" t="n">
-        <v>6783417</v>
+        <v>6783521</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3616,10 +3682,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131674853</v>
+        <v>131674807</v>
       </c>
       <c r="B31" t="n">
-        <v>8460</v>
+        <v>57162</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3627,30 +3693,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3660,10 +3725,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458513</v>
+        <v>458847</v>
       </c>
       <c r="R31" t="n">
-        <v>6783533</v>
+        <v>6783618</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,7 +3769,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3723,10 +3787,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131674857</v>
+        <v>131674808</v>
       </c>
       <c r="B32" t="n">
-        <v>8460</v>
+        <v>57162</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3734,30 +3798,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3767,10 +3830,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458876</v>
+        <v>458647</v>
       </c>
       <c r="R32" t="n">
-        <v>6783632</v>
+        <v>6783489</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3811,7 +3874,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3830,10 +3892,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131674858</v>
+        <v>131674845</v>
       </c>
       <c r="B33" t="n">
-        <v>8460</v>
+        <v>57165</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3841,30 +3903,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>102613</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3874,10 +3935,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458855</v>
+        <v>458496</v>
       </c>
       <c r="R33" t="n">
-        <v>6783588</v>
+        <v>6783417</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3918,7 +3979,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3937,7 +3997,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131674859</v>
+        <v>131674853</v>
       </c>
       <c r="B34" t="n">
         <v>8460</v>
@@ -3981,10 +4041,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458808</v>
+        <v>458513</v>
       </c>
       <c r="R34" t="n">
-        <v>6783574</v>
+        <v>6783533</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4044,7 +4104,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131674860</v>
+        <v>131674857</v>
       </c>
       <c r="B35" t="n">
         <v>8460</v>
@@ -4078,7 +4138,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4088,10 +4148,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458734</v>
+        <v>458876</v>
       </c>
       <c r="R35" t="n">
-        <v>6783516</v>
+        <v>6783632</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4151,7 +4211,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131674861</v>
+        <v>131674858</v>
       </c>
       <c r="B36" t="n">
         <v>8460</v>
@@ -4185,7 +4245,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4195,10 +4255,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458712</v>
+        <v>458855</v>
       </c>
       <c r="R36" t="n">
-        <v>6783546</v>
+        <v>6783588</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,7 +4318,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131674862</v>
+        <v>131674859</v>
       </c>
       <c r="B37" t="n">
         <v>8460</v>
@@ -4302,10 +4362,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>458637</v>
+        <v>458808</v>
       </c>
       <c r="R37" t="n">
-        <v>6783520</v>
+        <v>6783574</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4365,10 +4425,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131674915</v>
+        <v>131674860</v>
       </c>
       <c r="B38" t="n">
-        <v>8449</v>
+        <v>8460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4376,21 +4436,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4399,7 +4459,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4409,10 +4469,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>458671</v>
+        <v>458734</v>
       </c>
       <c r="R38" t="n">
-        <v>6783494</v>
+        <v>6783516</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4472,45 +4532,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131674846</v>
+        <v>131674861</v>
       </c>
       <c r="B39" t="n">
-        <v>79131</v>
+        <v>8460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>458738</v>
+        <v>458712</v>
       </c>
       <c r="R39" t="n">
-        <v>6783645</v>
+        <v>6783546</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,6 +4620,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4569,37 +4639,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131674849</v>
+        <v>131674862</v>
       </c>
       <c r="B40" t="n">
-        <v>79131</v>
+        <v>8460</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4607,10 +4683,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458875</v>
+        <v>458637</v>
       </c>
       <c r="R40" t="n">
-        <v>6783630</v>
+        <v>6783520</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4670,48 +4746,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131674850</v>
+        <v>135298239</v>
       </c>
       <c r="B41" t="n">
-        <v>79131</v>
+        <v>8460</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>458731</v>
+        <v>458578</v>
       </c>
       <c r="R41" t="n">
-        <v>6783519</v>
+        <v>6783446</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4735,12 +4816,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4751,61 +4842,80 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131674851</v>
+        <v>131674915</v>
       </c>
       <c r="B42" t="n">
-        <v>79131</v>
+        <v>8449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458704</v>
+        <v>458671</v>
       </c>
       <c r="R42" t="n">
-        <v>6783548</v>
+        <v>6783494</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4846,6 +4956,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4861,6 +4972,746 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135298241</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>458655</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6783510</v>
+      </c>
+      <c r="S43" t="n">
+        <v>7</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135298243</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>458606</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6783522</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135298245</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>458719</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6783522</v>
+      </c>
+      <c r="S45" t="n">
+        <v>7</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131674846</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>458738</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6783645</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131674849</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>458875</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6783630</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131674850</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>458731</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6783519</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131674851</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>458704</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6783548</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6098-2026 artfynd.xlsx
+++ b/artfynd/A 6098-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298248</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674890</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674901</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674902</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674904</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674905</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674906</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674907</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674908</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674909</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674910</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674911</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298242</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298247</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2221,6 +2296,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674866</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2322,6 +2402,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674867</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2419,6 +2504,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674773</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2524,6 +2614,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674821</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2629,6 +2724,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674827</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2734,6 +2834,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674828</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2839,6 +2944,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674829</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2944,6 +3054,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674830</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3049,6 +3164,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674832</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3154,6 +3274,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674833</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3259,6 +3384,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674841</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3364,6 +3494,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674795</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3469,6 +3604,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674799</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3574,6 +3714,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674803</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3679,6 +3824,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674804</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3784,6 +3934,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674807</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3889,6 +4044,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674808</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3994,6 +4154,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674845</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4101,6 +4266,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674853</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4208,6 +4378,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674857</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4315,6 +4490,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674858</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4422,6 +4602,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674859</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4529,6 +4714,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674860</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4636,6 +4826,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674861</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4743,6 +4938,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674862</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4865,6 +5065,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298239</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4972,6 +5177,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674915</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5088,6 +5298,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298241</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5204,6 +5419,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298243</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5320,6 +5540,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298245</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5417,6 +5642,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674846</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5518,6 +5748,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674849</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5615,6 +5850,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674850</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5712,8 +5952,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674851</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 6098-2026 artfynd.xlsx
+++ b/artfynd/A 6098-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135298248</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>135298242</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>135298247</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>135298239</v>
       </c>
       <c r="B41" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135298241</v>
       </c>
       <c r="B43" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>135298243</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>135298245</v>
       </c>
       <c r="B45" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 6098-2026 artfynd.xlsx
+++ b/artfynd/A 6098-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135298248</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>135298242</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>135298247</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135298241</v>
       </c>
       <c r="B43" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>135298243</v>
       </c>
       <c r="B44" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>135298245</v>
       </c>
       <c r="B45" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 6098-2026 artfynd.xlsx
+++ b/artfynd/A 6098-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131674890</v>
+        <v>135298248</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458690</v>
+        <v>458859</v>
       </c>
       <c r="R2" t="n">
-        <v>6783647</v>
+        <v>6783626</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,28 +771,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674890</t>
+          <t>https://artportalen.se/Sighting/135298248</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131674901</v>
+        <v>131674890</v>
       </c>
       <c r="B3" t="n">
         <v>79373</v>
@@ -817,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458843</v>
+        <v>458690</v>
       </c>
       <c r="R3" t="n">
-        <v>6783622</v>
+        <v>6783647</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,13 +908,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674901</t>
+          <t>https://artportalen.se/Sighting/131674890</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131674902</v>
+        <v>131674901</v>
       </c>
       <c r="B4" t="n">
         <v>79373</v>
@@ -919,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458812</v>
+        <v>458843</v>
       </c>
       <c r="R4" t="n">
-        <v>6783576</v>
+        <v>6783622</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,13 +1010,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674902</t>
+          <t>https://artportalen.se/Sighting/131674901</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131674904</v>
+        <v>131674902</v>
       </c>
       <c r="B5" t="n">
         <v>79373</v>
@@ -1021,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458628</v>
+        <v>458812</v>
       </c>
       <c r="R5" t="n">
-        <v>6783528</v>
+        <v>6783576</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,13 +1112,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674904</t>
+          <t>https://artportalen.se/Sighting/131674902</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131674905</v>
+        <v>131674904</v>
       </c>
       <c r="B6" t="n">
         <v>79373</v>
@@ -1123,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458618</v>
+        <v>458628</v>
       </c>
       <c r="R6" t="n">
-        <v>6783506</v>
+        <v>6783528</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,13 +1214,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674905</t>
+          <t>https://artportalen.se/Sighting/131674904</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131674906</v>
+        <v>131674905</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1225,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458582</v>
+        <v>458618</v>
       </c>
       <c r="R7" t="n">
-        <v>6783476</v>
+        <v>6783506</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,13 +1316,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674906</t>
+          <t>https://artportalen.se/Sighting/131674905</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131674907</v>
+        <v>131674906</v>
       </c>
       <c r="B8" t="n">
         <v>79373</v>
@@ -1327,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458562</v>
+        <v>458582</v>
       </c>
       <c r="R8" t="n">
-        <v>6783460</v>
+        <v>6783476</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,13 +1418,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674907</t>
+          <t>https://artportalen.se/Sighting/131674906</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131674908</v>
+        <v>131674907</v>
       </c>
       <c r="B9" t="n">
         <v>79373</v>
@@ -1429,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458548</v>
+        <v>458562</v>
       </c>
       <c r="R9" t="n">
-        <v>6783447</v>
+        <v>6783460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,13 +1520,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674908</t>
+          <t>https://artportalen.se/Sighting/131674907</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131674909</v>
+        <v>131674908</v>
       </c>
       <c r="B10" t="n">
         <v>79373</v>
@@ -1531,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458526</v>
+        <v>458548</v>
       </c>
       <c r="R10" t="n">
-        <v>6783438</v>
+        <v>6783447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,13 +1622,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674909</t>
+          <t>https://artportalen.se/Sighting/131674908</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131674910</v>
+        <v>131674909</v>
       </c>
       <c r="B11" t="n">
         <v>79373</v>
@@ -1633,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458917</v>
+        <v>458526</v>
       </c>
       <c r="R11" t="n">
-        <v>6783639</v>
+        <v>6783438</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,13 +1724,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674910</t>
+          <t>https://artportalen.se/Sighting/131674909</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131674911</v>
+        <v>131674910</v>
       </c>
       <c r="B12" t="n">
         <v>79373</v>
@@ -1735,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458855</v>
+        <v>458917</v>
       </c>
       <c r="R12" t="n">
-        <v>6783589</v>
+        <v>6783639</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,54 +1826,51 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674911</t>
+          <t>https://artportalen.se/Sighting/131674910</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131674866</v>
+        <v>131674911</v>
       </c>
       <c r="B13" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458846</v>
+        <v>458855</v>
       </c>
       <c r="R13" t="n">
-        <v>6783602</v>
+        <v>6783589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,7 +1911,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1902,57 +1928,54 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674866</t>
+          <t>https://artportalen.se/Sighting/131674911</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131674867</v>
+        <v>135298242</v>
       </c>
       <c r="B14" t="n">
-        <v>79130</v>
+        <v>79441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458832</v>
+        <v>458642</v>
       </c>
       <c r="R14" t="n">
-        <v>6783615</v>
+        <v>6783514</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1976,12 +1999,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1990,72 +2023,91 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674867</t>
+          <t>https://artportalen.se/Sighting/135298242</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131674773</v>
+        <v>135298247</v>
       </c>
       <c r="B15" t="n">
-        <v>79992</v>
+        <v>79441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458794</v>
+        <v>458859</v>
       </c>
       <c r="R15" t="n">
-        <v>6783576</v>
+        <v>6783622</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,12 +2131,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,63 +2157,78 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674773</t>
+          <t>https://artportalen.se/Sighting/135298247</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131674821</v>
+        <v>131674866</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>79130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2159,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458804</v>
+        <v>458846</v>
       </c>
       <c r="R16" t="n">
-        <v>6783648</v>
+        <v>6783602</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,6 +2280,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2220,48 +2298,43 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674821</t>
+          <t>https://artportalen.se/Sighting/131674866</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131674827</v>
+        <v>131674867</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>79130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2269,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458883</v>
+        <v>458832</v>
       </c>
       <c r="R17" t="n">
-        <v>6783596</v>
+        <v>6783615</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2313,6 +2386,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2330,59 +2404,51 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674827</t>
+          <t>https://artportalen.se/Sighting/131674867</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131674828</v>
+        <v>131674773</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458856</v>
+        <v>458794</v>
       </c>
       <c r="R18" t="n">
-        <v>6783589</v>
+        <v>6783576</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,13 +2506,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674828</t>
+          <t>https://artportalen.se/Sighting/131674773</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131674829</v>
+        <v>131674821</v>
       </c>
       <c r="B19" t="n">
         <v>57972</v>
@@ -2489,10 +2555,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458713</v>
+        <v>458804</v>
       </c>
       <c r="R19" t="n">
-        <v>6783543</v>
+        <v>6783648</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,13 +2616,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674829</t>
+          <t>https://artportalen.se/Sighting/131674821</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131674830</v>
+        <v>131674827</v>
       </c>
       <c r="B20" t="n">
         <v>57972</v>
@@ -2599,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458616</v>
+        <v>458883</v>
       </c>
       <c r="R20" t="n">
-        <v>6783487</v>
+        <v>6783596</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,13 +2726,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674830</t>
+          <t>https://artportalen.se/Sighting/131674827</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131674832</v>
+        <v>131674828</v>
       </c>
       <c r="B21" t="n">
         <v>57972</v>
@@ -2699,7 +2765,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2709,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458582</v>
+        <v>458856</v>
       </c>
       <c r="R21" t="n">
-        <v>6783476</v>
+        <v>6783589</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,13 +2836,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674832</t>
+          <t>https://artportalen.se/Sighting/131674828</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131674833</v>
+        <v>131674829</v>
       </c>
       <c r="B22" t="n">
         <v>57972</v>
@@ -2809,7 +2875,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2819,10 +2885,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458552</v>
+        <v>458713</v>
       </c>
       <c r="R22" t="n">
-        <v>6783452</v>
+        <v>6783543</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,13 +2946,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674833</t>
+          <t>https://artportalen.se/Sighting/131674829</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131674841</v>
+        <v>131674830</v>
       </c>
       <c r="B23" t="n">
         <v>57972</v>
@@ -2919,7 +2985,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2929,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458778</v>
+        <v>458616</v>
       </c>
       <c r="R23" t="n">
-        <v>6783537</v>
+        <v>6783487</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,33 +3056,33 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674841</t>
+          <t>https://artportalen.se/Sighting/131674830</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131674795</v>
+        <v>131674832</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3029,7 +3095,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3039,10 +3105,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458501</v>
+        <v>458582</v>
       </c>
       <c r="R24" t="n">
-        <v>6783418</v>
+        <v>6783476</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,16 +3166,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674795</t>
+          <t>https://artportalen.se/Sighting/131674832</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131674799</v>
+        <v>131674833</v>
       </c>
       <c r="B25" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,21 +3183,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3139,7 +3205,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3149,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458534</v>
+        <v>458552</v>
       </c>
       <c r="R25" t="n">
-        <v>6783516</v>
+        <v>6783452</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3210,16 +3276,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674799</t>
+          <t>https://artportalen.se/Sighting/131674833</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131674803</v>
+        <v>131674841</v>
       </c>
       <c r="B26" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,21 +3293,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3249,7 +3315,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3259,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458884</v>
+        <v>458778</v>
       </c>
       <c r="R26" t="n">
-        <v>6783621</v>
+        <v>6783537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,38 +3386,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674803</t>
+          <t>https://artportalen.se/Sighting/131674841</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131674804</v>
+        <v>131674795</v>
       </c>
       <c r="B27" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3359,7 +3425,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3369,10 +3435,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458703</v>
+        <v>458501</v>
       </c>
       <c r="R27" t="n">
-        <v>6783521</v>
+        <v>6783418</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,13 +3496,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674804</t>
+          <t>https://artportalen.se/Sighting/131674795</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131674807</v>
+        <v>131674799</v>
       </c>
       <c r="B28" t="n">
         <v>57162</v>
@@ -3469,7 +3535,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3479,10 +3545,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458847</v>
+        <v>458534</v>
       </c>
       <c r="R28" t="n">
-        <v>6783618</v>
+        <v>6783516</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,13 +3606,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674807</t>
+          <t>https://artportalen.se/Sighting/131674799</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131674808</v>
+        <v>131674803</v>
       </c>
       <c r="B29" t="n">
         <v>57162</v>
@@ -3589,10 +3655,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458647</v>
+        <v>458884</v>
       </c>
       <c r="R29" t="n">
-        <v>6783489</v>
+        <v>6783621</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,16 +3716,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674808</t>
+          <t>https://artportalen.se/Sighting/131674803</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131674845</v>
+        <v>131674804</v>
       </c>
       <c r="B30" t="n">
-        <v>57165</v>
+        <v>57162</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,21 +3733,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,7 +3755,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3699,10 +3765,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458496</v>
+        <v>458703</v>
       </c>
       <c r="R30" t="n">
-        <v>6783417</v>
+        <v>6783521</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3760,16 +3826,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674845</t>
+          <t>https://artportalen.se/Sighting/131674804</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131674853</v>
+        <v>131674807</v>
       </c>
       <c r="B31" t="n">
-        <v>8460</v>
+        <v>57162</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3777,30 +3843,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3810,10 +3875,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458513</v>
+        <v>458847</v>
       </c>
       <c r="R31" t="n">
-        <v>6783533</v>
+        <v>6783618</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,7 +3919,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3872,16 +3936,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674853</t>
+          <t>https://artportalen.se/Sighting/131674807</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131674857</v>
+        <v>131674808</v>
       </c>
       <c r="B32" t="n">
-        <v>8460</v>
+        <v>57162</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3889,30 +3953,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3922,10 +3985,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458876</v>
+        <v>458647</v>
       </c>
       <c r="R32" t="n">
-        <v>6783632</v>
+        <v>6783489</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3966,7 +4029,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3984,16 +4046,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674857</t>
+          <t>https://artportalen.se/Sighting/131674808</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131674858</v>
+        <v>131674845</v>
       </c>
       <c r="B33" t="n">
-        <v>8460</v>
+        <v>57165</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,30 +4063,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>102613</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4034,10 +4095,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458855</v>
+        <v>458496</v>
       </c>
       <c r="R33" t="n">
-        <v>6783588</v>
+        <v>6783417</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4078,7 +4139,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4096,13 +4156,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674858</t>
+          <t>https://artportalen.se/Sighting/131674845</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131674859</v>
+        <v>131674853</v>
       </c>
       <c r="B34" t="n">
         <v>8460</v>
@@ -4146,10 +4206,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458808</v>
+        <v>458513</v>
       </c>
       <c r="R34" t="n">
-        <v>6783574</v>
+        <v>6783533</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4208,13 +4268,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674859</t>
+          <t>https://artportalen.se/Sighting/131674853</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131674860</v>
+        <v>131674857</v>
       </c>
       <c r="B35" t="n">
         <v>8460</v>
@@ -4248,7 +4308,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4258,10 +4318,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458734</v>
+        <v>458876</v>
       </c>
       <c r="R35" t="n">
-        <v>6783516</v>
+        <v>6783632</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,13 +4380,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674860</t>
+          <t>https://artportalen.se/Sighting/131674857</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131674861</v>
+        <v>131674858</v>
       </c>
       <c r="B36" t="n">
         <v>8460</v>
@@ -4360,7 +4420,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4370,10 +4430,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458712</v>
+        <v>458855</v>
       </c>
       <c r="R36" t="n">
-        <v>6783546</v>
+        <v>6783588</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4432,13 +4492,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674861</t>
+          <t>https://artportalen.se/Sighting/131674858</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131674862</v>
+        <v>131674859</v>
       </c>
       <c r="B37" t="n">
         <v>8460</v>
@@ -4482,10 +4542,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>458637</v>
+        <v>458808</v>
       </c>
       <c r="R37" t="n">
-        <v>6783520</v>
+        <v>6783574</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4544,16 +4604,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674862</t>
+          <t>https://artportalen.se/Sighting/131674859</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131674915</v>
+        <v>131674860</v>
       </c>
       <c r="B38" t="n">
-        <v>8449</v>
+        <v>8460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4561,21 +4621,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4584,7 +4644,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4594,10 +4654,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>458671</v>
+        <v>458734</v>
       </c>
       <c r="R38" t="n">
-        <v>6783494</v>
+        <v>6783516</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4656,51 +4716,60 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674915</t>
+          <t>https://artportalen.se/Sighting/131674860</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131674846</v>
+        <v>131674861</v>
       </c>
       <c r="B39" t="n">
-        <v>79131</v>
+        <v>8460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>458738</v>
+        <v>458712</v>
       </c>
       <c r="R39" t="n">
-        <v>6783645</v>
+        <v>6783546</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4741,6 +4810,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4758,43 +4828,49 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674846</t>
+          <t>https://artportalen.se/Sighting/131674861</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131674849</v>
+        <v>131674862</v>
       </c>
       <c r="B40" t="n">
-        <v>79131</v>
+        <v>8460</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4802,10 +4878,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458875</v>
+        <v>458637</v>
       </c>
       <c r="R40" t="n">
-        <v>6783630</v>
+        <v>6783520</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4864,54 +4940,59 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674849</t>
+          <t>https://artportalen.se/Sighting/131674862</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131674850</v>
+        <v>135298239</v>
       </c>
       <c r="B41" t="n">
-        <v>79131</v>
+        <v>8461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>458731</v>
+        <v>458578</v>
       </c>
       <c r="R41" t="n">
-        <v>6783519</v>
+        <v>6783446</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4935,12 +5016,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4951,66 +5042,85 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674850</t>
+          <t>https://artportalen.se/Sighting/135298239</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131674851</v>
+        <v>131674915</v>
       </c>
       <c r="B42" t="n">
-        <v>79131</v>
+        <v>8449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458704</v>
+        <v>458671</v>
       </c>
       <c r="R42" t="n">
-        <v>6783548</v>
+        <v>6783494</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5051,6 +5161,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5067,6 +5178,781 @@
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674915</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135298241</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>458655</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6783510</v>
+      </c>
+      <c r="S43" t="n">
+        <v>7</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298241</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135298243</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>458606</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6783522</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298243</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135298245</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>458719</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6783522</v>
+      </c>
+      <c r="S45" t="n">
+        <v>7</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298245</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131674846</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>458738</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6783645</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674846</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131674849</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>458875</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6783630</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674849</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131674850</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>458731</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6783519</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674850</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131674851</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>458704</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6783548</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131674851</t>
         </is>
@@ -5115,6 +6001,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6098-2026 artfynd.xlsx
+++ b/artfynd/A 6098-2026 artfynd.xlsx
@@ -5188,7 +5188,7 @@
         <v>135298241</v>
       </c>
       <c r="B43" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>135298243</v>
       </c>
       <c r="B44" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>135298245</v>
       </c>
       <c r="B45" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
